--- a/profiles.xlsx
+++ b/profiles.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Dr Transition\kb\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Dr Transition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E10315C-72D3-4AFA-B50B-3CDE13DA0306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A30AE1-4C9D-404D-A0E9-F6CFE146C3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{B3F6DA94-93D2-4AC3-829A-E2C6BB0F81CB}"/>
   </bookViews>
@@ -274,7 +274,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,30 +282,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -313,36 +299,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -659,324 +621,328 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A70043-5D96-40EB-BCCF-757568EF506F}">
   <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" t="s">
         <v>77</v>
       </c>
     </row>
